--- a/output/pdf_financials_xlsx/PNE.xlsx
+++ b/output/pdf_financials_xlsx/PNE.xlsx
@@ -883,31 +883,31 @@
         <v>0</v>
       </c>
       <c r="I9" s="3" t="n">
-        <v>0</v>
+        <v>0.005083</v>
       </c>
       <c r="J9" s="3" t="n">
-        <v>0</v>
+        <v>0.008821000000000001</v>
       </c>
       <c r="K9" s="3" t="n">
-        <v>0</v>
+        <v>0.010152</v>
       </c>
       <c r="L9" s="3" t="n">
-        <v>0</v>
+        <v>0.007357</v>
       </c>
       <c r="M9" s="3" t="n">
-        <v>0</v>
+        <v>0.017009</v>
       </c>
       <c r="N9" s="3" t="n">
-        <v>0</v>
+        <v>0.03576</v>
       </c>
       <c r="O9" s="3" t="n">
-        <v>0</v>
+        <v>0.019963</v>
       </c>
       <c r="P9" s="3" t="n">
-        <v>0</v>
+        <v>0.015426</v>
       </c>
       <c r="Q9" s="3" t="n">
-        <v>0</v>
+        <v>0.014041</v>
       </c>
     </row>
     <row r="10">
@@ -942,31 +942,31 @@
         <v>0.000615</v>
       </c>
       <c r="I10" s="3" t="n">
-        <v>0.001919</v>
+        <v>0.007002</v>
       </c>
       <c r="J10" s="3" t="n">
-        <v>0.007034</v>
+        <v>0.015855</v>
       </c>
       <c r="K10" s="3" t="n">
-        <v>0</v>
+        <v>0.010152</v>
       </c>
       <c r="L10" s="3" t="n">
-        <v>0</v>
+        <v>0.007357</v>
       </c>
       <c r="M10" s="3" t="n">
-        <v>0</v>
+        <v>0.017009</v>
       </c>
       <c r="N10" s="3" t="n">
-        <v>0</v>
+        <v>0.03576</v>
       </c>
       <c r="O10" s="3" t="n">
-        <v>0</v>
+        <v>0.019963</v>
       </c>
       <c r="P10" s="3" t="n">
-        <v>0</v>
+        <v>0.015426</v>
       </c>
       <c r="Q10" s="3" t="n">
-        <v>0</v>
+        <v>0.014041</v>
       </c>
     </row>
     <row r="11">
@@ -1003,31 +1003,31 @@
         <v>0.070469</v>
       </c>
       <c r="I11" s="3" t="n">
-        <v>0.07224800000000001</v>
+        <v>0.067165</v>
       </c>
       <c r="J11" s="3" t="n">
-        <v>0.104018</v>
+        <v>0.095197</v>
       </c>
       <c r="K11" s="3" t="n">
-        <v>0.115076</v>
+        <v>0.104924</v>
       </c>
       <c r="L11" s="3" t="n">
-        <v>0.100063</v>
+        <v>0.092706</v>
       </c>
       <c r="M11" s="3" t="n">
-        <v>0.150706</v>
+        <v>0.133697</v>
       </c>
       <c r="N11" s="3" t="n">
-        <v>0.274728</v>
+        <v>0.238968</v>
       </c>
       <c r="O11" s="3" t="n">
-        <v>0.17626</v>
+        <v>0.156297</v>
       </c>
       <c r="P11" s="3" t="n">
-        <v>0.180201</v>
+        <v>0.164775</v>
       </c>
       <c r="Q11" s="3" t="n">
-        <v>0.164552</v>
+        <v>0.150511</v>
       </c>
     </row>
     <row r="12">
@@ -57272,7 +57272,11 @@
           <t>Royalty expense</t>
         </is>
       </c>
-      <c r="D511" t="inlineStr"/>
+      <c r="D511" t="inlineStr">
+        <is>
+          <t>OtherOperatingExpenses</t>
+        </is>
+      </c>
       <c r="E511" t="inlineStr">
         <is>
           <t>-</t>
@@ -57309,31 +57313,31 @@
         </is>
       </c>
       <c r="L511" s="5" t="n">
-        <v>-0.005083</v>
+        <v>0.005083</v>
       </c>
       <c r="M511" s="5" t="n">
-        <v>-0.008821000000000001</v>
+        <v>0.008821000000000001</v>
       </c>
       <c r="N511" s="5" t="n">
-        <v>-0.010152</v>
+        <v>0.010152</v>
       </c>
       <c r="O511" s="5" t="n">
-        <v>-0.007357</v>
+        <v>0.007357</v>
       </c>
       <c r="P511" s="5" t="n">
-        <v>-0.017009</v>
+        <v>0.017009</v>
       </c>
       <c r="Q511" s="5" t="n">
-        <v>-0.03576</v>
+        <v>0.03576</v>
       </c>
       <c r="R511" s="5" t="n">
-        <v>-0.019963</v>
+        <v>0.019963</v>
       </c>
       <c r="S511" s="5" t="n">
-        <v>-0.015426</v>
+        <v>0.015426</v>
       </c>
       <c r="T511" s="5" t="n">
-        <v>-0.014041</v>
+        <v>0.014041</v>
       </c>
     </row>
     <row r="512">

--- a/output/pdf_financials_xlsx/PNE.xlsx
+++ b/output/pdf_financials_xlsx/PNE.xlsx
@@ -936,37 +936,37 @@
         </is>
       </c>
       <c r="G10" s="3" t="n">
-        <v>0.000353</v>
+        <v>0.039251</v>
       </c>
       <c r="H10" s="3" t="n">
-        <v>0.000615</v>
+        <v>0.072547</v>
       </c>
       <c r="I10" s="3" t="n">
-        <v>0.007002</v>
+        <v>0.108681</v>
       </c>
       <c r="J10" s="3" t="n">
-        <v>0.015855</v>
+        <v>0.172565</v>
       </c>
       <c r="K10" s="3" t="n">
-        <v>0.010152</v>
+        <v>0.162104</v>
       </c>
       <c r="L10" s="3" t="n">
-        <v>0.007357</v>
+        <v>0.143884</v>
       </c>
       <c r="M10" s="3" t="n">
-        <v>0.017009</v>
+        <v>0.119926</v>
       </c>
       <c r="N10" s="3" t="n">
-        <v>0.03576</v>
+        <v>0.152169</v>
       </c>
       <c r="O10" s="3" t="n">
-        <v>0.019963</v>
+        <v>0.173701</v>
       </c>
       <c r="P10" s="3" t="n">
-        <v>0.015426</v>
+        <v>0.207439</v>
       </c>
       <c r="Q10" s="3" t="n">
-        <v>0.014041</v>
+        <v>0.179779</v>
       </c>
     </row>
     <row r="11">
@@ -997,37 +997,37 @@
         </is>
       </c>
       <c r="G11" s="3" t="n">
-        <v>0.034342</v>
+        <v>-0.004556</v>
       </c>
       <c r="H11" s="3" t="n">
-        <v>0.070469</v>
+        <v>-0.001463</v>
       </c>
       <c r="I11" s="3" t="n">
-        <v>0.067165</v>
+        <v>-0.034514</v>
       </c>
       <c r="J11" s="3" t="n">
-        <v>0.095197</v>
+        <v>-0.061513</v>
       </c>
       <c r="K11" s="3" t="n">
-        <v>0.104924</v>
+        <v>-0.047028</v>
       </c>
       <c r="L11" s="3" t="n">
-        <v>0.092706</v>
+        <v>-0.043821</v>
       </c>
       <c r="M11" s="3" t="n">
-        <v>0.133697</v>
+        <v>0.03078</v>
       </c>
       <c r="N11" s="3" t="n">
-        <v>0.238968</v>
+        <v>0.122559</v>
       </c>
       <c r="O11" s="3" t="n">
-        <v>0.156297</v>
+        <v>0.002559</v>
       </c>
       <c r="P11" s="3" t="n">
-        <v>0.164775</v>
+        <v>-0.027238</v>
       </c>
       <c r="Q11" s="3" t="n">
-        <v>0.150511</v>
+        <v>-0.015227</v>
       </c>
     </row>
     <row r="12">
@@ -1037,10 +1037,10 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>0</v>
+        <v>0.128935</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>0</v>
+        <v>0.006097</v>
       </c>
       <c r="D12" s="1" t="inlineStr">
         <is>
@@ -1077,10 +1077,10 @@
         <v>0</v>
       </c>
       <c r="N12" s="3" t="n">
-        <v>0</v>
+        <v>0.0005</v>
       </c>
       <c r="O12" s="3" t="n">
-        <v>0</v>
+        <v>0.002212</v>
       </c>
       <c r="P12" s="3" t="n">
         <v>0</v>
@@ -1992,10 +1992,10 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>-7.541868</v>
+        <v>-7.670803</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>-2.822276</v>
+        <v>-2.828373</v>
       </c>
       <c r="D27" s="1" t="inlineStr">
         <is>
@@ -2034,10 +2034,10 @@
         <v>0.03078</v>
       </c>
       <c r="N27" s="3" t="n">
-        <v>0.122559</v>
+        <v>0.122059</v>
       </c>
       <c r="O27" s="3" t="n">
-        <v>0.002559</v>
+        <v>0.000347</v>
       </c>
       <c r="P27" s="3" t="n">
         <v>-0.027238</v>
@@ -2112,10 +2112,10 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>-7.541868</v>
+        <v>-7.670803</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>-2.822276</v>
+        <v>-2.828373</v>
       </c>
       <c r="D29" s="1" t="inlineStr">
         <is>
@@ -2154,10 +2154,10 @@
         <v>0.071774</v>
       </c>
       <c r="N29" s="3" t="n">
-        <v>0.166633</v>
+        <v>0.166133</v>
       </c>
       <c r="O29" s="3" t="n">
-        <v>0.046487</v>
+        <v>0.044275</v>
       </c>
       <c r="P29" s="3" t="n">
         <v>0.026431</v>
@@ -2173,10 +2173,10 @@
         </is>
       </c>
       <c r="B30" s="3" t="n">
-        <v>-1169.876774545816</v>
+        <v>-1189.8768676164</v>
       </c>
       <c r="C30" s="3" t="n">
-        <v>-551.4336458860469</v>
+        <v>-552.6249152512568</v>
       </c>
       <c r="D30" s="1" t="inlineStr">
         <is>
@@ -2215,10 +2215,10 @@
         <v>47.62517749790984</v>
       </c>
       <c r="N30" s="3" t="n">
-        <v>60.65381031420169</v>
+        <v>60.47181211962377</v>
       </c>
       <c r="O30" s="3" t="n">
-        <v>26.37410643367753</v>
+        <v>25.11914217633042</v>
       </c>
       <c r="P30" s="3" t="n">
         <v>14.66751016919995</v>
@@ -2363,13 +2363,13 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>2.624556</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>1.372643</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>1.333553</v>
       </c>
       <c r="E34" s="1" t="inlineStr">
         <is>
@@ -2391,19 +2391,19 @@
         <v>0.000833</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>0</v>
+        <v>0.000148</v>
       </c>
       <c r="K34" s="3" t="n">
-        <v>0</v>
+        <v>0.001075</v>
       </c>
       <c r="L34" s="3" t="n">
-        <v>0</v>
+        <v>0.003563</v>
       </c>
       <c r="M34" s="3" t="n">
-        <v>0</v>
+        <v>0.006874</v>
       </c>
       <c r="N34" s="3" t="n">
-        <v>0</v>
+        <v>0.054428</v>
       </c>
       <c r="O34" s="3" t="n">
         <v>0</v>
@@ -2412,7 +2412,7 @@
         <v>0</v>
       </c>
       <c r="Q34" s="3" t="n">
-        <v>0</v>
+        <v>0.004066</v>
       </c>
     </row>
     <row r="35">
@@ -2481,13 +2481,13 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>2.624556</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>1.372643</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>1.333553</v>
       </c>
       <c r="E36" s="1" t="inlineStr">
         <is>
@@ -2509,19 +2509,19 @@
         <v>0.000833</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>0</v>
+        <v>0.000148</v>
       </c>
       <c r="K36" s="3" t="n">
-        <v>0</v>
+        <v>0.001075</v>
       </c>
       <c r="L36" s="3" t="n">
-        <v>0</v>
+        <v>0.003563</v>
       </c>
       <c r="M36" s="3" t="n">
-        <v>0</v>
+        <v>0.006874</v>
       </c>
       <c r="N36" s="3" t="n">
-        <v>0</v>
+        <v>0.054428</v>
       </c>
       <c r="O36" s="3" t="n">
         <v>0</v>
@@ -2530,7 +2530,7 @@
         <v>0</v>
       </c>
       <c r="Q36" s="3" t="n">
-        <v>0</v>
+        <v>0.004066</v>
       </c>
     </row>
     <row r="37">
@@ -3189,13 +3189,13 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>2.654158</v>
+        <v>0.029602</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>1.388988</v>
+        <v>0.016345</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>1.349898</v>
+        <v>0.016345</v>
       </c>
       <c r="E48" s="1" t="inlineStr">
         <is>
@@ -3217,19 +3217,19 @@
         <v>0.00684</v>
       </c>
       <c r="J48" s="3" t="n">
-        <v>0.008933999999999999</v>
+        <v>0.008786</v>
       </c>
       <c r="K48" s="3" t="n">
-        <v>0.007502</v>
+        <v>0.006427</v>
       </c>
       <c r="L48" s="3" t="n">
-        <v>0.007417</v>
+        <v>0.003854</v>
       </c>
       <c r="M48" s="3" t="n">
-        <v>0.01032</v>
+        <v>0.003446</v>
       </c>
       <c r="N48" s="3" t="n">
-        <v>0.058366</v>
+        <v>0.003938</v>
       </c>
       <c r="O48" s="3" t="n">
         <v>0.007529</v>
@@ -3238,7 +3238,7 @@
         <v>0.005722</v>
       </c>
       <c r="Q48" s="3" t="n">
-        <v>0.00855</v>
+        <v>0.004484</v>
       </c>
     </row>
     <row r="49">
@@ -8586,7 +8586,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -18732,7 +18732,7 @@
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
@@ -30964,7 +30964,7 @@
       </c>
       <c r="D236" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E236" t="inlineStr">
@@ -35150,7 +35150,7 @@
       </c>
       <c r="D279" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E279" s="5" t="n">
@@ -58430,7 +58430,7 @@
       </c>
       <c r="D524" t="inlineStr">
         <is>
-          <t>TotalExpenses</t>
+          <t>OperatingExpense</t>
         </is>
       </c>
       <c r="E524" t="inlineStr">
@@ -60234,7 +60234,7 @@
       </c>
       <c r="D543" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E543" t="inlineStr">
@@ -66438,7 +66438,7 @@
       </c>
       <c r="D608" t="inlineStr">
         <is>
-          <t>TotalExpenses</t>
+          <t>OperatingExpense</t>
         </is>
       </c>
       <c r="E608" t="inlineStr">
@@ -67690,7 +67690,7 @@
       </c>
       <c r="D621" t="inlineStr">
         <is>
-          <t>TotalExpenses</t>
+          <t>OperatingExpense</t>
         </is>
       </c>
       <c r="E621" t="inlineStr">
@@ -69038,7 +69038,7 @@
       </c>
       <c r="D635" t="inlineStr">
         <is>
-          <t>TotalExpenses</t>
+          <t>OperatingExpense</t>
         </is>
       </c>
       <c r="E635" t="inlineStr">
@@ -73986,7 +73986,7 @@
       </c>
       <c r="D687" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E687" t="inlineStr">
@@ -80512,7 +80512,7 @@
       </c>
       <c r="D755" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E755" s="5" t="n">

--- a/output/pdf_financials_xlsx/PNE.xlsx
+++ b/output/pdf_financials_xlsx/PNE.xlsx
@@ -7001,7 +7001,7 @@
         <v>0</v>
       </c>
       <c r="D112" s="3" t="n">
-        <v>0</v>
+        <v>0.006456</v>
       </c>
       <c r="E112" s="3" t="n">
         <v>0</v>
@@ -53522,7 +53522,11 @@
           <t>Loss on disposal of property and equipment</t>
         </is>
       </c>
-      <c r="D472" t="inlineStr"/>
+      <c r="D472" t="inlineStr">
+        <is>
+          <t>SaleOfPPE</t>
+        </is>
+      </c>
       <c r="E472" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/PNE.xlsx
+++ b/output/pdf_financials_xlsx/PNE.xlsx
@@ -1362,7 +1362,7 @@
         <v>0.010257</v>
       </c>
       <c r="J17" s="3" t="n">
-        <v>0.011126</v>
+        <v>-0.011126</v>
       </c>
       <c r="K17" s="3" t="n">
         <v>0.020836</v>
@@ -1751,10 +1751,8 @@
       <c r="C23" s="3" t="n">
         <v>-2.822276</v>
       </c>
-      <c r="D23" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D23" s="3" t="n">
+        <v>-0.372776</v>
       </c>
       <c r="E23" s="1" t="inlineStr">
         <is>
@@ -4177,15 +4175,11 @@
       <c r="D64" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="E64" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F64" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E64" s="3" t="n">
+        <v>0.012</v>
+      </c>
+      <c r="F64" s="3" t="n">
+        <v>2.139</v>
       </c>
       <c r="G64" s="3" t="n">
         <v>0.008579</v>
@@ -4354,24 +4348,20 @@
       <c r="D67" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="E67" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F67" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E67" s="3" t="n">
+        <v>0.08699999999999999</v>
+      </c>
+      <c r="F67" s="3" t="n">
+        <v>1.674</v>
       </c>
       <c r="G67" s="3" t="n">
-        <v>0</v>
+        <v>0.001538</v>
       </c>
       <c r="H67" s="3" t="n">
-        <v>0</v>
+        <v>0.006413</v>
       </c>
       <c r="I67" s="3" t="n">
-        <v>0</v>
+        <v>0.006303</v>
       </c>
       <c r="J67" s="3" t="n">
         <v>0</v>
@@ -4424,13 +4414,13 @@
         </is>
       </c>
       <c r="G68" s="3" t="n">
-        <v>0.008579</v>
+        <v>0.010117</v>
       </c>
       <c r="H68" s="3" t="n">
-        <v>0.01128</v>
+        <v>0.017693</v>
       </c>
       <c r="I68" s="3" t="n">
-        <v>0.009978000000000001</v>
+        <v>0.016281</v>
       </c>
       <c r="J68" s="3" t="n">
         <v>0.021319</v>
@@ -4560,19 +4550,19 @@
         <v>0</v>
       </c>
       <c r="M70" s="3" t="n">
-        <v>0</v>
+        <v>0.00105</v>
       </c>
       <c r="N70" s="3" t="n">
-        <v>0</v>
+        <v>0.001002</v>
       </c>
       <c r="O70" s="3" t="n">
-        <v>0</v>
+        <v>0.001119</v>
       </c>
       <c r="P70" s="3" t="n">
-        <v>0</v>
+        <v>0.001287</v>
       </c>
       <c r="Q70" s="3" t="n">
-        <v>0</v>
+        <v>0.001352</v>
       </c>
     </row>
     <row r="71">
@@ -4619,19 +4609,19 @@
         <v>0</v>
       </c>
       <c r="M71" s="3" t="n">
-        <v>0</v>
+        <v>0.00105</v>
       </c>
       <c r="N71" s="3" t="n">
-        <v>0</v>
+        <v>0.001002</v>
       </c>
       <c r="O71" s="3" t="n">
-        <v>0</v>
+        <v>0.001119</v>
       </c>
       <c r="P71" s="3" t="n">
-        <v>0</v>
+        <v>0.001287</v>
       </c>
       <c r="Q71" s="3" t="n">
-        <v>0</v>
+        <v>0.001352</v>
       </c>
     </row>
     <row r="72">
@@ -4837,10 +4827,10 @@
         </is>
       </c>
       <c r="G75" s="3" t="n">
-        <v>0.0002</v>
+        <v>0</v>
       </c>
       <c r="H75" s="3" t="n">
-        <v>0.047755</v>
+        <v>0.041342</v>
       </c>
       <c r="I75" s="3" t="n">
         <v>0</v>
@@ -4855,19 +4845,19 @@
         <v>0.002466</v>
       </c>
       <c r="M75" s="3" t="n">
-        <v>0.00495</v>
+        <v>0.0039</v>
       </c>
       <c r="N75" s="3" t="n">
-        <v>0.007901999999999999</v>
+        <v>0.0069</v>
       </c>
       <c r="O75" s="3" t="n">
-        <v>0.020661</v>
+        <v>0.019542</v>
       </c>
       <c r="P75" s="3" t="n">
-        <v>0.027502</v>
+        <v>0.026215</v>
       </c>
       <c r="Q75" s="3" t="n">
-        <v>0.013857</v>
+        <v>0.012505</v>
       </c>
     </row>
     <row r="76">
@@ -5167,30 +5157,20 @@
           <t>-</t>
         </is>
       </c>
-      <c r="M80" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N80" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O80" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="P80" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="Q80" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="M80" s="3" t="n">
+        <v>0.02311858734422476</v>
+      </c>
+      <c r="N80" s="3" t="n">
+        <v>0.007492821249102656</v>
+      </c>
+      <c r="O80" s="3" t="n">
+        <v>0.01119806260507565</v>
+      </c>
+      <c r="P80" s="3" t="n">
+        <v>0.02369118621603711</v>
+      </c>
+      <c r="Q80" s="3" t="n">
+        <v>0.03812854282410671</v>
       </c>
     </row>
     <row r="81">
@@ -6227,12 +6207,10 @@
         </is>
       </c>
       <c r="C99" s="3" t="n">
-        <v>-2.822276</v>
-      </c>
-      <c r="D99" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-0.452136</v>
+      </c>
+      <c r="D99" s="3" t="n">
+        <v>-0.372776</v>
       </c>
       <c r="E99" s="1" t="inlineStr">
         <is>
@@ -7213,10 +7191,10 @@
         <v>0</v>
       </c>
       <c r="O115" s="3" t="n">
-        <v>0</v>
+        <v>0.000315</v>
       </c>
       <c r="P115" s="3" t="n">
-        <v>0</v>
+        <v>0.000191</v>
       </c>
       <c r="Q115" s="3" t="n">
         <v>0</v>
@@ -9472,7 +9450,11 @@
           <t>Lease liabilities 8</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr"/>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>CurrentCapitalLeaseObligation</t>
+        </is>
+      </c>
       <c r="E12" t="inlineStr">
         <is>
           <t>-</t>
@@ -11100,7 +11082,11 @@
           <t>Lease liabilities 9</t>
         </is>
       </c>
-      <c r="D30" t="inlineStr"/>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>CurrentCapitalLeaseObligation</t>
+        </is>
+      </c>
       <c r="E30" t="inlineStr">
         <is>
           <t>-</t>
@@ -11952,7 +11938,11 @@
           <t>Lease liabilities 11</t>
         </is>
       </c>
-      <c r="D39" t="inlineStr"/>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>CurrentCapitalLeaseObligation</t>
+        </is>
+      </c>
       <c r="E39" t="inlineStr">
         <is>
           <t>-</t>
@@ -12140,7 +12130,11 @@
           <t>Lease liabilities 10</t>
         </is>
       </c>
-      <c r="D41" t="inlineStr"/>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>CurrentCapitalLeaseObligation</t>
+        </is>
+      </c>
       <c r="E41" t="inlineStr">
         <is>
           <t>-</t>
@@ -38854,7 +38848,11 @@
           <t>Proceeds on sale of investments</t>
         </is>
       </c>
-      <c r="D318" t="inlineStr"/>
+      <c r="D318" t="inlineStr">
+        <is>
+          <t>SaleOfInvestment</t>
+        </is>
+      </c>
       <c r="E318" t="inlineStr">
         <is>
           <t>-</t>
@@ -45516,7 +45514,11 @@
           <t>Deferred income tax expense 11</t>
         </is>
       </c>
-      <c r="D388" t="inlineStr"/>
+      <c r="D388" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E388" t="inlineStr">
         <is>
           <t>-</t>
@@ -47236,7 +47238,11 @@
           <t>Deferred income tax expense (recovery) 10</t>
         </is>
       </c>
-      <c r="D406" t="inlineStr"/>
+      <c r="D406" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E406" t="inlineStr">
         <is>
           <t>-</t>
@@ -48674,7 +48680,11 @@
           <t>Deferred tax recovery 10</t>
         </is>
       </c>
-      <c r="D421" t="inlineStr"/>
+      <c r="D421" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E421" t="inlineStr">
         <is>
           <t>-</t>
@@ -50482,7 +50492,11 @@
           <t>Deferred tax expense (recovery)</t>
         </is>
       </c>
-      <c r="D440" t="inlineStr"/>
+      <c r="D440" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E440" t="inlineStr">
         <is>
           <t>-</t>
@@ -52570,7 +52584,11 @@
           <t>Deferred tax expense</t>
         </is>
       </c>
-      <c r="D462" t="inlineStr"/>
+      <c r="D462" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E462" t="inlineStr">
         <is>
           <t>-</t>
@@ -55448,7 +55466,11 @@
           <t>Net loss from continuing operations</t>
         </is>
       </c>
-      <c r="D492" t="inlineStr"/>
+      <c r="D492" t="inlineStr">
+        <is>
+          <t>NetIncomeFromContinuingOperations</t>
+        </is>
+      </c>
       <c r="E492" t="inlineStr">
         <is>
           <t>-</t>
@@ -67888,7 +67910,11 @@
           <t>Deferred income tax recovery (expense) 10</t>
         </is>
       </c>
-      <c r="D623" t="inlineStr"/>
+      <c r="D623" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E623" t="inlineStr">
         <is>
           <t>-</t>
